--- a/outputs/llm_eval/topical_yjx/sig/News_Author_correlation_results.xlsx
+++ b/outputs/llm_eval/topical_yjx/sig/News_Author_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.3441006747714217</v>
+        <v>0.4940220843164407</v>
       </c>
       <c r="C2">
-        <v>0.3444046497506417</v>
+        <v>0.4802503840948975</v>
       </c>
       <c r="D2">
-        <v>0.2919826286828536</v>
+        <v>0.4401223723217983</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.280368417885648</v>
+        <v>0.3269010563195146</v>
       </c>
       <c r="C3">
-        <v>0.3088861729145201</v>
+        <v>0.3385633765196875</v>
       </c>
       <c r="D3">
-        <v>0.237528003678588</v>
+        <v>0.2971628870163905</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,18 +445,27 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.4377176001519053</v>
+        <v>0.6111769161525084</v>
       </c>
       <c r="C4">
-        <v>0.4683128665779133</v>
+        <v>0.6054464719814235</v>
       </c>
       <c r="D4">
-        <v>0.369356570622329</v>
+        <v>0.5578628001083531</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0.5533320959479985</v>
+      </c>
+      <c r="C5">
+        <v>0.556051981810913</v>
+      </c>
+      <c r="D5">
+        <v>0.5390498524628192</v>
       </c>
     </row>
   </sheetData>
